--- a/database_penyimpanan_aman/database_billing_tax.xlsx
+++ b/database_penyimpanan_aman/database_billing_tax.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Nomor PO Rujukan</t>
+          <t>Nomor PO</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -474,40 +474,45 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Informasi Bank</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Nilai Invoice</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>PPN Nominal</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>PPh Nominal</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Total Netto</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Kena PPN</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Kena PPh</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Tarif PPh</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Update Terakhir</t>
         </is>
@@ -526,17 +531,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4500011586</t>
+          <t>4500011588</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1000024082.0</t>
+          <t>1000024082</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -569,30 +574,35 @@
           <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>24150000</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2656500</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>483000</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>26323500</v>
-      </c>
-      <c r="P2" t="b">
-        <v>1</v>
       </c>
       <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
         <v>2</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-08-26 22:04:58</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-08-27 07:39:39</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_billing_tax.xlsx
+++ b/database_penyimpanan_aman/database_billing_tax.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,31 +517,40 @@
           <t>Update Terakhir</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Gunakan Professional Sum</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Add Cost</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4500011588</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1000024082</t>
-        </is>
+          <t>010/BSS-JOB/IX/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7203250036</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4500010848</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1000025700</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,17 +570,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton Periode Bulan Juli 2026</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -580,16 +589,16 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>24150000</v>
+        <v>46683000</v>
       </c>
       <c r="N2" t="n">
-        <v>2656500</v>
+        <v>5135130</v>
       </c>
       <c r="O2" t="n">
-        <v>483000</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>26323500</v>
+        <v>51818130</v>
       </c>
       <c r="Q2" t="b">
         <v>1</v>
@@ -598,12 +607,112 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-27 07:39:39</t>
-        </is>
+          <t>2026-08-27 14:14:15</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>012/BSS_JOB/IX/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4500011586</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1000456710</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>002.796.802.3-081.000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>24150000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2656500</v>
+      </c>
+      <c r="O3" t="n">
+        <v>120750</v>
+      </c>
+      <c r="P3" t="n">
+        <v>26685750</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-08-27 15:57:15</t>
+        </is>
+      </c>
+      <c r="U3" t="b">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3150000</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_billing_tax.xlsx
+++ b/database_penyimpanan_aman/database_billing_tax.xlsx
@@ -484,52 +484,52 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>Gunakan Professional Sum</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Add Cost</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>PPN Nominal</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PPh Nominal</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Total Netto</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Kena PPN</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Kena PPh</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Tarif PPh</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Update Terakhir</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Gunakan Professional Sum</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Add Cost</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Management Fee</t>
         </is>
       </c>
     </row>
@@ -540,17 +540,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7203250036</v>
+        <v>7201250141</v>
       </c>
       <c r="C2" t="n">
-        <v>4500010848</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1000025700</v>
+        <v>4500011586</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1000025700</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -592,31 +594,37 @@
         <v>46683000</v>
       </c>
       <c r="N2" t="n">
-        <v>5135130</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5135130</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>51818130</v>
       </c>
-      <c r="Q2" t="b">
+      <c r="T2" t="b">
         <v>1</v>
       </c>
-      <c r="R2" t="b">
+      <c r="U2" t="b">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-08-27 14:14:15</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:04:28</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -624,20 +632,14 @@
           <t>012/BSS_JOB/IX/2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4500011586</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1000456710</t>
-        </is>
+      <c r="B3" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4500011586</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1000456710</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -683,36 +685,36 @@
         <v>24150000</v>
       </c>
       <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2656500</v>
       </c>
-      <c r="O3" t="n">
-        <v>120750</v>
-      </c>
-      <c r="P3" t="n">
-        <v>26685750</v>
-      </c>
-      <c r="Q3" t="b">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>26806500</v>
+      </c>
+      <c r="T3" t="b">
         <v>1</v>
-      </c>
-      <c r="R3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-08-27 15:57:15</t>
-        </is>
       </c>
       <c r="U3" t="b">
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3150000</v>
+        <v>0</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-08-27 17:04:12</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_billing_tax.xlsx
+++ b/database_penyimpanan_aman/database_billing_tax.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,18 +536,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/IX/2026</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>7201250141</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4500011586</v>
+          <t>012/BSS-JOB/IX/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4500011586</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1000025700</t>
+          <t>100004581</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -572,17 +576,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton Periode Bulan Juli 2026</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -591,7 +595,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>46683000</v>
+        <v>12600000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -603,117 +607,26 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5135130</v>
+        <v>1386000</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>51818130</v>
+        <v>13986000</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-08-27 17:04:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>012/BSS_JOB/IX/2026</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>7201250141</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4500011586</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1000456710</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>002.796.802.3-081.000</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>24150000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3150000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2656500</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>26806500</v>
-      </c>
-      <c r="T3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" t="b">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2026-08-27 17:04:12</t>
+          <t>2026-09-07 22:18:12</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_billing_tax.xlsx
+++ b/database_penyimpanan_aman/database_billing_tax.xlsx
@@ -539,20 +539,14 @@
           <t>012/BSS-JOB/IX/2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4500011586</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>100004581</t>
-        </is>
+      <c r="B2" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4500011586</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100004581</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -626,7 +620,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:18:12</t>
+          <t>2026-09-08 15:39:20</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_billing_tax.xlsx
+++ b/database_penyimpanan_aman/database_billing_tax.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,21 +536,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/IX/2026</t>
+          <t>036/BSS-JOB/II/2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="C2" t="n">
-        <v>4500011586</v>
+        <v>4500010745</v>
       </c>
       <c r="D2" t="n">
-        <v>100004581</v>
+        <v>1000024198</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>006/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -570,17 +570,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>12600000</v>
+        <v>51177360</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -601,13 +601,13 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1386000</v>
+        <v>5629509.6</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>13986000</v>
+        <v>56806869.6</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
@@ -620,7 +620,286 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-09-08 15:39:20</t>
+          <t>2026-09-10 20:13:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/II/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7207250142</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4500010746</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1000024199</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>002.796.802.3-081.000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>73803990</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>8118438.9</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>81922428.90000001</v>
+      </c>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-10 20:15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>126/BSS-JOB/VI/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4500011203</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1000025162</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>002.796.802.3-081.000</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>6919250</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>761117.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7680367.5</v>
+      </c>
+      <c r="T4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-09-10 21:57:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>127/BSS-JOB/VI/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4500011236</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1000025165</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>004/BSS-JOB/WS/IV/2026</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>002.796.802.3-081.000</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>890007884.9999999</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>773919900</v>
+      </c>
+      <c r="P5" t="n">
+        <v>116087984.9999999</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>97900867.34999999</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>987908752.3499999</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-10 22:11:26</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_billing_tax.xlsx
+++ b/database_penyimpanan_aman/database_billing_tax.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,20 +812,14 @@
           <t>127/BSS-JOB/VI/2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4500011236</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1000025165</t>
-        </is>
+      <c r="B5" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4500011236</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1000025165</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -900,6 +894,103 @@
       <c r="W5" t="inlineStr">
         <is>
           <t>2026-09-10 22:11:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/II/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4500010750</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1000024200</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>004/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>002.796.802.3-081.000</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Bank Name :&lt;/b&gt; BANK RAKYAT INDONESIA (PERSERO) Tbk.&lt;br&gt;&lt;b&gt;Branch :&lt;/b&gt; Cabang Luwuk&lt;br&gt;&lt;b&gt;Account No :&lt;/b&gt; 0167 0167 8888 303&lt;br&gt;&lt;b&gt;Account Name :&lt;/b&gt; PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>30507750</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3355852.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>33863602.5</v>
+      </c>
+      <c r="T6" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:28:14</t>
         </is>
       </c>
     </row>
